--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283191</v>
+        <v>121283193</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>97041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691959</v>
+        <v>692142</v>
       </c>
       <c r="R2" t="n">
-        <v>7138924</v>
+        <v>7138826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283193</v>
+        <v>121283191</v>
       </c>
       <c r="B3" t="n">
-        <v>97031</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692142</v>
+        <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138826</v>
+        <v>7138924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283186</v>
+        <v>121283189</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>97041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691926</v>
+        <v>691959</v>
       </c>
       <c r="R4" t="n">
-        <v>7139146</v>
+        <v>7138932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283189</v>
+        <v>121283209</v>
       </c>
       <c r="B5" t="n">
-        <v>97031</v>
+        <v>58208</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691959</v>
+        <v>691951</v>
       </c>
       <c r="R5" t="n">
-        <v>7138932</v>
+        <v>7138827</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283209</v>
+        <v>121283186</v>
       </c>
       <c r="B6" t="n">
-        <v>58205</v>
+        <v>91973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691951</v>
+        <v>691926</v>
       </c>
       <c r="R6" t="n">
-        <v>7138827</v>
+        <v>7139146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283193</v>
+        <v>121283189</v>
       </c>
       <c r="B2" t="n">
         <v>97041</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692142</v>
+        <v>691959</v>
       </c>
       <c r="R2" t="n">
-        <v>7138826</v>
+        <v>7138932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283191</v>
+        <v>121283209</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>58208</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691959</v>
+        <v>691951</v>
       </c>
       <c r="R3" t="n">
-        <v>7138924</v>
+        <v>7138827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283189</v>
+        <v>121283193</v>
       </c>
       <c r="B4" t="n">
         <v>97041</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691959</v>
+        <v>692142</v>
       </c>
       <c r="R4" t="n">
-        <v>7138932</v>
+        <v>7138826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283209</v>
+        <v>121283186</v>
       </c>
       <c r="B5" t="n">
-        <v>58208</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691951</v>
+        <v>691926</v>
       </c>
       <c r="R5" t="n">
-        <v>7138827</v>
+        <v>7139146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283186</v>
+        <v>121283191</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691926</v>
+        <v>691959</v>
       </c>
       <c r="R6" t="n">
-        <v>7139146</v>
+        <v>7138924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283189</v>
+        <v>121283209</v>
       </c>
       <c r="B2" t="n">
-        <v>97041</v>
+        <v>58208</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691959</v>
+        <v>691951</v>
       </c>
       <c r="R2" t="n">
-        <v>7138932</v>
+        <v>7138827</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283209</v>
+        <v>121283189</v>
       </c>
       <c r="B3" t="n">
-        <v>58208</v>
+        <v>97041</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691951</v>
+        <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138827</v>
+        <v>7138932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283209</v>
+        <v>121283186</v>
       </c>
       <c r="B2" t="n">
-        <v>58208</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691951</v>
+        <v>691926</v>
       </c>
       <c r="R2" t="n">
-        <v>7138827</v>
+        <v>7139146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283189</v>
+        <v>121283191</v>
       </c>
       <c r="B3" t="n">
-        <v>97041</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138932</v>
+        <v>7138924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283193</v>
+        <v>121283209</v>
       </c>
       <c r="B4" t="n">
-        <v>97041</v>
+        <v>58208</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692142</v>
+        <v>691951</v>
       </c>
       <c r="R4" t="n">
-        <v>7138826</v>
+        <v>7138827</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283186</v>
+        <v>121283193</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>97054</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691926</v>
+        <v>692142</v>
       </c>
       <c r="R5" t="n">
-        <v>7139146</v>
+        <v>7138826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283191</v>
+        <v>121283189</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>97054</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
         <v>691959</v>
       </c>
       <c r="R6" t="n">
-        <v>7138924</v>
+        <v>7138932</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283186</v>
+        <v>121283191</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691926</v>
+        <v>691959</v>
       </c>
       <c r="R2" t="n">
-        <v>7139146</v>
+        <v>7138924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283191</v>
+        <v>121283189</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>97055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138924</v>
+        <v>7138932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283209</v>
+        <v>121283186</v>
       </c>
       <c r="B4" t="n">
-        <v>58208</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691951</v>
+        <v>691926</v>
       </c>
       <c r="R4" t="n">
-        <v>7138827</v>
+        <v>7139146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283193</v>
+        <v>121283209</v>
       </c>
       <c r="B5" t="n">
-        <v>97054</v>
+        <v>58208</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692142</v>
+        <v>691951</v>
       </c>
       <c r="R5" t="n">
-        <v>7138826</v>
+        <v>7138827</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283189</v>
+        <v>121283193</v>
       </c>
       <c r="B6" t="n">
-        <v>97054</v>
+        <v>97055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691959</v>
+        <v>692142</v>
       </c>
       <c r="R6" t="n">
-        <v>7138932</v>
+        <v>7138826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283191</v>
+        <v>121283189</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>691959</v>
       </c>
       <c r="R2" t="n">
-        <v>7138924</v>
+        <v>7138932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283189</v>
+        <v>121283191</v>
       </c>
       <c r="B3" t="n">
-        <v>97055</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138932</v>
+        <v>7138924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283186</v>
+        <v>121283209</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>58211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691926</v>
+        <v>691951</v>
       </c>
       <c r="R4" t="n">
-        <v>7139146</v>
+        <v>7138827</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283209</v>
+        <v>121283193</v>
       </c>
       <c r="B5" t="n">
-        <v>58208</v>
+        <v>97058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691951</v>
+        <v>692142</v>
       </c>
       <c r="R5" t="n">
-        <v>7138827</v>
+        <v>7138826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283193</v>
+        <v>121283186</v>
       </c>
       <c r="B6" t="n">
-        <v>97055</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692142</v>
+        <v>691926</v>
       </c>
       <c r="R6" t="n">
-        <v>7138826</v>
+        <v>7139146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283189</v>
+        <v>121283209</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
+        <v>58211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691959</v>
+        <v>691951</v>
       </c>
       <c r="R2" t="n">
-        <v>7138932</v>
+        <v>7138827</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283191</v>
+        <v>121283189</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138924</v>
+        <v>7138932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283209</v>
+        <v>121283191</v>
       </c>
       <c r="B4" t="n">
-        <v>58211</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691951</v>
+        <v>691959</v>
       </c>
       <c r="R4" t="n">
-        <v>7138827</v>
+        <v>7138924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283209</v>
+        <v>121283186</v>
       </c>
       <c r="B2" t="n">
-        <v>58211</v>
+        <v>91995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691951</v>
+        <v>691926</v>
       </c>
       <c r="R2" t="n">
-        <v>7138827</v>
+        <v>7139146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283189</v>
+        <v>121283209</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>58212</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691959</v>
+        <v>691951</v>
       </c>
       <c r="R3" t="n">
-        <v>7138932</v>
+        <v>7138827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283191</v>
+        <v>121283189</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>97064</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,7 +930,7 @@
         <v>691959</v>
       </c>
       <c r="R4" t="n">
-        <v>7138924</v>
+        <v>7138932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>121283193</v>
       </c>
       <c r="B5" t="n">
-        <v>97058</v>
+        <v>97064</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283186</v>
+        <v>121283191</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
+        <v>79226</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691926</v>
+        <v>691959</v>
       </c>
       <c r="R6" t="n">
-        <v>7139146</v>
+        <v>7138924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121283186</v>
       </c>
       <c r="B2" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121283209</v>
       </c>
       <c r="B3" t="n">
-        <v>58212</v>
+        <v>58213</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>121283189</v>
       </c>
       <c r="B4" t="n">
-        <v>97064</v>
+        <v>97065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>121283193</v>
       </c>
       <c r="B5" t="n">
-        <v>97064</v>
+        <v>97065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>121283191</v>
       </c>
       <c r="B6" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283209</v>
+        <v>121283189</v>
       </c>
       <c r="B3" t="n">
-        <v>58213</v>
+        <v>97065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691951</v>
+        <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138827</v>
+        <v>7138932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283189</v>
+        <v>121283193</v>
       </c>
       <c r="B4" t="n">
         <v>97065</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691959</v>
+        <v>692142</v>
       </c>
       <c r="R4" t="n">
-        <v>7138932</v>
+        <v>7138826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283193</v>
+        <v>121283209</v>
       </c>
       <c r="B5" t="n">
-        <v>97065</v>
+        <v>58213</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692142</v>
+        <v>691951</v>
       </c>
       <c r="R5" t="n">
-        <v>7138826</v>
+        <v>7138827</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283186</v>
+        <v>121283209</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>58213</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691926</v>
+        <v>691951</v>
       </c>
       <c r="R2" t="n">
-        <v>7139146</v>
+        <v>7138827</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283189</v>
+        <v>121283191</v>
       </c>
       <c r="B3" t="n">
-        <v>97065</v>
+        <v>79227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>691959</v>
       </c>
       <c r="R3" t="n">
-        <v>7138932</v>
+        <v>7138924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283193</v>
+        <v>121283189</v>
       </c>
       <c r="B4" t="n">
         <v>97065</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692142</v>
+        <v>691959</v>
       </c>
       <c r="R4" t="n">
-        <v>7138826</v>
+        <v>7138932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283209</v>
+        <v>121283186</v>
       </c>
       <c r="B5" t="n">
-        <v>58213</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691951</v>
+        <v>691926</v>
       </c>
       <c r="R5" t="n">
-        <v>7138827</v>
+        <v>7139146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283191</v>
+        <v>121283193</v>
       </c>
       <c r="B6" t="n">
-        <v>79227</v>
+        <v>97065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691959</v>
+        <v>692142</v>
       </c>
       <c r="R6" t="n">
-        <v>7138924</v>
+        <v>7138826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283209</v>
+        <v>121283191</v>
       </c>
       <c r="B2" t="n">
-        <v>58213</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691951</v>
+        <v>691959</v>
       </c>
       <c r="R2" t="n">
-        <v>7138827</v>
+        <v>7138924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283191</v>
+        <v>121283186</v>
       </c>
       <c r="B3" t="n">
-        <v>79227</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691959</v>
+        <v>691926</v>
       </c>
       <c r="R3" t="n">
-        <v>7138924</v>
+        <v>7139146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283186</v>
+        <v>121283193</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>97065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691926</v>
+        <v>692142</v>
       </c>
       <c r="R5" t="n">
-        <v>7139146</v>
+        <v>7138826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283193</v>
+        <v>121283209</v>
       </c>
       <c r="B6" t="n">
-        <v>97065</v>
+        <v>58213</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692142</v>
+        <v>691951</v>
       </c>
       <c r="R6" t="n">
-        <v>7138826</v>
+        <v>7138827</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36155-2019 artfynd.xlsx
+++ b/artfynd/A 36155-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283191</v>
+        <v>121283186</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>92001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691959</v>
+        <v>691926</v>
       </c>
       <c r="R2" t="n">
-        <v>7138924</v>
+        <v>7139146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283186</v>
+        <v>121283209</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>58214</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691926</v>
+        <v>691951</v>
       </c>
       <c r="R3" t="n">
-        <v>7139146</v>
+        <v>7138827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283189</v>
+        <v>121283193</v>
       </c>
       <c r="B4" t="n">
-        <v>97065</v>
+        <v>97070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691959</v>
+        <v>692142</v>
       </c>
       <c r="R4" t="n">
-        <v>7138932</v>
+        <v>7138826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283193</v>
+        <v>121283189</v>
       </c>
       <c r="B5" t="n">
-        <v>97065</v>
+        <v>97070</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692142</v>
+        <v>691959</v>
       </c>
       <c r="R5" t="n">
-        <v>7138826</v>
+        <v>7138932</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283209</v>
+        <v>121283191</v>
       </c>
       <c r="B6" t="n">
-        <v>58213</v>
+        <v>79232</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691951</v>
+        <v>691959</v>
       </c>
       <c r="R6" t="n">
-        <v>7138827</v>
+        <v>7138924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
